--- a/config/Nykaa_instruction.xlsx
+++ b/config/Nykaa_instruction.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA712DEC-F703-45BB-A7C9-CECBACDA25FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184155AE-0872-4665-BC7A-122C3CB80697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Mapping-Kids Casual Shoes" sheetId="1" r:id="rId1"/>
+    <sheet name="Mapping-Kids Sandal" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Kids Casual Shoes'!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Sandal'!$A$1:$D$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
